--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17278660</v>
+        <v>135495569</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källviksberget, Mpd</t>
+          <t>Junibosand, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633442</v>
+        <v>633447</v>
       </c>
       <c r="R2" t="n">
         <v>6904015</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,35 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17278668</v>
+        <v>135495574</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>80351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,41 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrvikssand, Mpd</t>
+          <t>Junibosand, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633212</v>
+        <v>633480</v>
       </c>
       <c r="R3" t="n">
-        <v>6903943</v>
+        <v>6903967</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På äldre grov asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,35 +858,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Rekreationsområde</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17279033</v>
+        <v>135495570</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,41 +885,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrvikssand, Mpd</t>
+          <t>Junibosand, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633212</v>
+        <v>633443</v>
       </c>
       <c r="R4" t="n">
-        <v>6903943</v>
+        <v>6904012</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,57 +955,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Rekreationsområde</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17278761</v>
+        <v>17278660</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,14 +1006,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvikssand, Mpd</t>
+          <t>Källviksberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633212</v>
+        <v>633442</v>
       </c>
       <c r="R5" t="n">
-        <v>6903943</v>
+        <v>6904015</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1093,7 +1059,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Rekreationsområde</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1112,6 +1078,2297 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17278668</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrvikssand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633212</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6903943</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Rekreationsområde</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135495572</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79753</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6903970</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135495588</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>633415</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6904055</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>17279033</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrvikssand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>633212</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6903943</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Rekreationsområde</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135495575</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>633479</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6903966</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135495578</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>633480</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6903966</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135495571</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>633450</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6904030</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135495567</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>633457</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6904080</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135495564</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>633473</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6904095</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135495563</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>633473</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6904096</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135495582</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>633411</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6903928</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135495576</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>633481</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6903970</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135495585</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>633213</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6903883</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135495580</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>633445</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6903923</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135495581</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>633430</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6903917</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135495584</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>633403</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6903930</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135495589</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>633444</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6904081</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135495577</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>633480</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6903965</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135495583</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>633408</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6903930</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17278761</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrvikssand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>633212</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6903943</v>
+      </c>
+      <c r="S25" t="n">
+        <v>100</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Rekreationsområde</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135495579</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633478</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6903966</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135495587</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>633199</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6904019</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135495586</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>633202</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6904023</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495569</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495574</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495570</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278668</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495572</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495588</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17279033</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495575</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495578</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495571</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495567</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495564</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495563</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495582</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2289,6 +2369,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495576</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2386,6 +2471,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495585</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2483,6 +2573,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495580</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495581</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2677,6 +2777,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495584</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2774,6 +2879,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495589</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495577</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2968,6 +3083,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495583</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3078,6 +3198,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278761</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3175,6 +3300,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495579</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3272,6 +3402,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495587</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3369,8 +3504,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495586</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495569</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495574</v>
       </c>
       <c r="B3" t="n">
-        <v>80351</v>
+        <v>80389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>135495570</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135495572</v>
       </c>
       <c r="B7" t="n">
-        <v>79753</v>
+        <v>79791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>135495588</v>
       </c>
       <c r="B8" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>135495575</v>
       </c>
       <c r="B10" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135495578</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>135495571</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135495567</v>
       </c>
       <c r="B13" t="n">
-        <v>58410</v>
+        <v>58415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135495564</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>135495563</v>
       </c>
       <c r="B15" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>135495582</v>
       </c>
       <c r="B16" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135495576</v>
       </c>
       <c r="B17" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135495585</v>
       </c>
       <c r="B18" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135495580</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135495581</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135495584</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135495589</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135495577</v>
       </c>
       <c r="B23" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135495583</v>
       </c>
       <c r="B24" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>135495579</v>
       </c>
       <c r="B26" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135495587</v>
       </c>
       <c r="B27" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>135495586</v>
       </c>
       <c r="B28" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495569</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495574</v>
       </c>
       <c r="B3" t="n">
-        <v>80389</v>
+        <v>80416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>135495570</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135495572</v>
       </c>
       <c r="B7" t="n">
-        <v>79791</v>
+        <v>79818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>135495588</v>
       </c>
       <c r="B8" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>135495575</v>
       </c>
       <c r="B10" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>135495582</v>
       </c>
       <c r="B16" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135495576</v>
       </c>
       <c r="B17" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135495585</v>
       </c>
       <c r="B18" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135495580</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135495581</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135495584</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135495589</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135495577</v>
       </c>
       <c r="B23" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135495583</v>
       </c>
       <c r="B24" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>135495579</v>
       </c>
       <c r="B26" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135495587</v>
       </c>
       <c r="B27" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>135495586</v>
       </c>
       <c r="B28" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17278660</v>
+        <v>135495569</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källviksberget, Mpd</t>
+          <t>Junibosand, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633442</v>
+        <v>633447</v>
       </c>
       <c r="R2" t="n">
         <v>6904015</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,40 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17278660</t>
+          <t>https://artportalen.se/Sighting/135495569</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17278668</v>
+        <v>135495574</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>80419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,41 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrvikssand, Mpd</t>
+          <t>Junibosand, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633212</v>
+        <v>633480</v>
       </c>
       <c r="R3" t="n">
-        <v>6903943</v>
+        <v>6903967</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På äldre grov asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,40 +868,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Rekreationsområde</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17278668</t>
+          <t>https://artportalen.se/Sighting/135495574</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17279033</v>
+        <v>135495570</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>92048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,41 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrvikssand, Mpd</t>
+          <t>Junibosand, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633212</v>
+        <v>633443</v>
       </c>
       <c r="R4" t="n">
-        <v>6903943</v>
+        <v>6904012</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,62 +970,53 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Rekreationsområde</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17279033</t>
+          <t>https://artportalen.se/Sighting/135495570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17278761</v>
+        <v>17278660</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,14 +1026,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvikssand, Mpd</t>
+          <t>Källviksberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633212</v>
+        <v>633442</v>
       </c>
       <c r="R5" t="n">
-        <v>6903943</v>
+        <v>6904015</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1113,7 +1079,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Rekreationsområde</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1134,7 +1100,2413 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/17278660</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17278668</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrvikssand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633212</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6903943</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Rekreationsområde</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278668</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135495572</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79821</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6903970</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495572</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135495588</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>633415</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6904055</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495588</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>17279033</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrvikssand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>633212</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6903943</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Rekreationsområde</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17279033</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135495575</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>633479</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6903966</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495575</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135495578</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>633480</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6903966</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495578</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135495571</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>633450</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6904030</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495571</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135495567</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58415</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>633457</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6904080</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495567</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135495564</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>633473</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6904095</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495564</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135495563</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>633473</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6904096</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495563</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135495582</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>633411</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6903928</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495582</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135495576</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99309</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>633481</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6903970</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495576</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135495585</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99309</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>633213</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6903883</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495585</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135495580</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>633445</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6903923</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495580</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135495581</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>633430</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6903917</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495581</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135495584</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>633403</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6903930</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495584</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135495589</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>633444</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6904081</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495589</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135495577</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106411</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>633480</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6903965</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495577</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135495583</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>633408</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6903930</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495583</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17278761</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrvikssand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>633212</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6903943</v>
+      </c>
+      <c r="S25" t="n">
+        <v>100</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Rekreationsområde</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/17278761</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135495579</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633478</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6903966</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495579</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135495587</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>633199</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6904019</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495587</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135495586</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Junibosand, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>633202</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6904023</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495586</t>
         </is>
       </c>
     </row>
@@ -1144,6 +3516,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>135495570</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>135495582</v>
       </c>
       <c r="B16" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135495576</v>
       </c>
       <c r="B17" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135495585</v>
       </c>
       <c r="B18" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135495580</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135495581</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135495584</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135495589</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135495577</v>
       </c>
       <c r="B23" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135495583</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>135495579</v>
       </c>
       <c r="B26" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135495587</v>
       </c>
       <c r="B27" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>135495586</v>
       </c>
       <c r="B28" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495569</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495574</v>
       </c>
       <c r="B3" t="n">
-        <v>80419</v>
+        <v>80421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>135495570</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135495572</v>
       </c>
       <c r="B7" t="n">
-        <v>79821</v>
+        <v>79823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>135495588</v>
       </c>
       <c r="B8" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>135495575</v>
       </c>
       <c r="B10" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135495578</v>
       </c>
       <c r="B11" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>135495571</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135495567</v>
       </c>
       <c r="B13" t="n">
-        <v>58415</v>
+        <v>58417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135495564</v>
       </c>
       <c r="B14" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>135495563</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>135495582</v>
       </c>
       <c r="B16" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135495576</v>
       </c>
       <c r="B17" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135495585</v>
       </c>
       <c r="B18" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135495580</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135495581</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135495584</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135495589</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135495577</v>
       </c>
       <c r="B23" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135495583</v>
       </c>
       <c r="B24" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>135495579</v>
       </c>
       <c r="B26" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135495587</v>
       </c>
       <c r="B27" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>135495586</v>
       </c>
       <c r="B28" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 30462-2026 artfynd.xlsx
+++ b/artfynd/A 30462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495569</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495574</v>
       </c>
       <c r="B3" t="n">
-        <v>80421</v>
+        <v>80422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>135495570</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135495572</v>
       </c>
       <c r="B7" t="n">
-        <v>79823</v>
+        <v>79824</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>135495588</v>
       </c>
       <c r="B8" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>135495575</v>
       </c>
       <c r="B10" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>135495582</v>
       </c>
       <c r="B16" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135495576</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135495585</v>
       </c>
       <c r="B18" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>135495580</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135495581</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135495584</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135495589</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135495577</v>
       </c>
       <c r="B23" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135495583</v>
       </c>
       <c r="B24" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>135495579</v>
       </c>
       <c r="B26" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135495587</v>
       </c>
       <c r="B27" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>135495586</v>
       </c>
       <c r="B28" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
